--- a/output/collection_mis_report.xlsx
+++ b/output/collection_mis_report.xlsx
@@ -716,14 +716,14 @@
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>LOAN COLLECTION ANALYZER — EXECUTIVE MIS REPORT</t>
+          <t>LOANPULSE ANALYTICS — EXECUTIVE COLLECTION MIS REPORT</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Vastu Housing Finance — Collection Strategy &amp; Delinquency Portfolio Review</t>
+          <t>Retail Lending Portfolio Risk &amp; Delinquency Performance Review</t>
         </is>
       </c>
     </row>
